--- a/bizconfig/static-xlsx/moba/pixel_moba/skill_level.xlsx
+++ b/bizconfig/static-xlsx/moba/pixel_moba/skill_level.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,75 +705,41 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>外键 -&gt; skill.id</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>等级 1-9</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>冷却时间毫秒</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>法力消耗(无消耗留 0)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>施法距离(像素)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AOE 半径,无 AOE 留空,仅服务端</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>基础伤害,代入 effect 公式,仅服务端</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>基础治疗,仅服务端</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>buff 持续时间,仅服务端</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>弹道速度(像素/秒),instant 留空,仅服务端</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>物攻加成比(0.5=50% 物攻),仅服务端</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>法攻加成比,仅服务端</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>最大生命加成比(部分技能用),仅服务端</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>该技能吸血率(0-1),仅服务端</t>
-        </is>
+      <c r="A5" t="n">
+        <v>5001</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>48</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -781,26 +747,28 @@
         <v>5001</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>8000</v>
+        <v>11000</v>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>48</v>
+      </c>
       <c r="G6" t="n">
-        <v>80</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3000</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -817,26 +785,28 @@
         <v>5001</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>48</v>
+      </c>
       <c r="G7" t="n">
-        <v>130</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3000</v>
+      </c>
       <c r="K7" t="n">
-        <v>0.55</v>
+        <v>1.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -850,37 +820,844 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="D8" t="n">
         <v>80</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>96</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5002</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>96</v>
+      </c>
+      <c r="G9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5002</v>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D10" t="n">
         <v>120</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
-        <v>400</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>96</v>
+      </c>
+      <c r="G10" t="n">
+        <v>70</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5011</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>60</v>
+      </c>
+      <c r="E11" t="n">
+        <v>256</v>
+      </c>
+      <c r="F11" t="n">
+        <v>96</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5011</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9500</v>
+      </c>
+      <c r="D12" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" t="n">
+        <v>256</v>
+      </c>
+      <c r="F12" t="n">
+        <v>96</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5011</v>
+      </c>
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E13" t="n">
+        <v>256</v>
+      </c>
+      <c r="F13" t="n">
+        <v>96</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5012</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>384</v>
+      </c>
+      <c r="F14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>500</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5012</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>110</v>
+      </c>
+      <c r="E15" t="n">
+        <v>384</v>
+      </c>
+      <c r="F15" t="n">
+        <v>32</v>
+      </c>
+      <c r="G15" t="n">
+        <v>45</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>500</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5012</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>140</v>
+      </c>
+      <c r="E16" t="n">
+        <v>384</v>
+      </c>
+      <c r="F16" t="n">
+        <v>32</v>
+      </c>
+      <c r="G16" t="n">
+        <v>90</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>500</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5021</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" t="n">
+        <v>384</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>700</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5021</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D18" t="n">
+        <v>45</v>
+      </c>
+      <c r="E18" t="n">
+        <v>384</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>70</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>700</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5021</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E19" t="n">
+        <v>384</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>130</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>700</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5022</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5022</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>55</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5022</v>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>70</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5003</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5004</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5013</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5014</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5023</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5024</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
